--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -97,8 +97,11 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Description: Contains information protected by copyright of SNOMED International. Any use of SNOMED CT in Austria requires a valid affiliate license or sublicense. The corresponding license is free of charge, provided that the use only takes place in Austria and fulfills the conditions of the Affiliate License Agreement. Affiliate licenses can be requested directly from the respective NRC via the Member Licensing and Distribution Service (MLDS).https://wiki.hl7.at/index.php?title=SCT:SNOMED_CT
-Beschreibung: Enthält durch SNOMED International urheberrechtlich geschützte Information. Jede Verwendung von SNOMED CT in Österreich erfordert eine aufrechte Affiliate Lizenz oder eine Sublizenz. Die entsprechende Lizenz ist kostenlos, vorausgesetzt die Verwendung findet nur in Österreich statt und erfüllt die Bedingungen des Affiliate License Agreements. Affiliate Lizenzen können über das Member Licensing and Distribution Service (MLDS) direkt beim jeweiligen NRC beantragt werden.https://wiki.hl7.at/index.php?title=SCT:SNOMED_CT</t>
+    <t xml:space="preserve">Description: Contains information protected by copyright of SNOMED International. Any use of SNOMED CT in Austria requires a valid affiliate license or sublicense. The corresponding license is free of charge, provided that the use only takes place in Austria and fulfills the conditions of the Affiliate License Agreement. Affiliate licenses can be requested directly from the respective NRC via the Member Licensing and Distribution Service (MLDS).https://wiki.hl7.at/index.php?title=SCT:SNOMED_CT
+This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc.
+Beschreibung: Enthält durch SNOMED International urheberrechtlich geschützte Information. Jede Verwendung von SNOMED CT in Österreich erfordert eine aufrechte Affiliate Lizenz oder eine Sublizenz. Die entsprechende Lizenz ist kostenlos, vorausgesetzt die Verwendung findet nur in Österreich statt und erfüllt die Bedingungen des Affiliate License Agreements. Affiliate Lizenzen können über das Member Licensing and Distribution Service (MLDS) direkt beim jeweiligen NRC beantragt werden.https://wiki.hl7.at/index.php?title=SCT:SNOMED_CT
+Dieses Material enthält Inhalte aus LOINC (http://loinc.org). LOINC ist urheberrechtlich geschützt © 1995-2020 durch das Regenstrief Institute, Inc. und den Logical Observation Identifiers Names and Codes (LOINC) Committee und steht kostenfrei unter der Lizenz unter http://loinc.org/license zur Verfügung. LOINC® ist eine eingetragene Marke des Regenstrief Institute, Inc. in den Vereinigten Staaten.
+</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,12 +111,6 @@
   </si>
   <si>
     <t>Concept</t>
-  </si>
-  <si>
-    <t>66266-8</t>
-  </si>
-  <si>
-    <t>Time doing this activity</t>
   </si>
   <si>
     <t>66270-0</t>
@@ -411,7 +405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -436,26 +430,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -482,10 +468,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +484,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
